--- a/output/Data and Chart Outputs/ireland_gas_supply_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gas_supply_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland gas supply by source (monthly average) (to Mar/26)</a:t>
             </a:r>
           </a:p>
@@ -801,7 +802,7 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>51.88844678571429</v>
+        <v>51.88844678571428</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -863,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>93.08110193333333</v>
+        <v>93.08110193333336</v>
       </c>
     </row>
     <row r="8">
@@ -891,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>91.49608412903225</v>
+        <v>91.49608412903224</v>
       </c>
     </row>
     <row r="10">
@@ -913,13 +914,13 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>45.35071067741936</v>
+        <v>45.35071067741935</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>90.77313606451612</v>
+        <v>90.77313606451614</v>
       </c>
     </row>
     <row r="12">
@@ -941,7 +942,7 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>45.53461029032258</v>
+        <v>45.53461029032259</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -955,7 +956,7 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>45.29863767741935</v>
+        <v>45.29863767741936</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -983,7 +984,7 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>43.48369222580645</v>
+        <v>43.48369222580644</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -997,7 +998,7 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>42.851332</v>
+        <v>42.85133199999999</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1025,7 +1026,7 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>40.75030373333333</v>
+        <v>40.75030373333334</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1067,7 +1068,7 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>39.30162416666667</v>
+        <v>39.30162416666666</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1087,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>94.23781351612902</v>
+        <v>94.23781351612901</v>
       </c>
     </row>
     <row r="24">
@@ -1207,7 +1208,7 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>17.3204025483871</v>
+        <v>17.32040254838709</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1235,7 +1236,7 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>34.1855907</v>
+        <v>34.18559070000001</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1255,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>103.0742370645161</v>
+        <v>103.0742370645162</v>
       </c>
     </row>
     <row r="36">
@@ -1263,7 +1264,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>33.23423666666667</v>
+        <v>33.23423666666666</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1283,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>110.918960483871</v>
+        <v>110.9189604838709</v>
       </c>
     </row>
     <row r="38">
@@ -1319,7 +1320,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>32.04054696774193</v>
+        <v>32.04054696774194</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1395,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>87.78872774193549</v>
+        <v>87.78872774193547</v>
       </c>
     </row>
     <row r="46">
@@ -1423,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>119.8232616774194</v>
+        <v>119.8232616774193</v>
       </c>
     </row>
     <row r="48">
@@ -1445,7 +1446,7 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>28.14798709677419</v>
+        <v>28.1479870967742</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1459,7 +1460,7 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>27.22278206451613</v>
+        <v>27.22278206451612</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1515,7 +1516,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>26.89465003225806</v>
+        <v>26.89465003225807</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1529,13 +1530,13 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>20.24507783333333</v>
+        <v>20.24507783333334</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>96.59046903333333</v>
+        <v>96.59046903333335</v>
       </c>
     </row>
     <row r="56">
@@ -1543,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>25.82068880645161</v>
+        <v>25.82068880645162</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1571,7 +1572,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>24.57852826666667</v>
+        <v>24.57852826666666</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1599,13 +1600,13 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>24.9135729</v>
+        <v>24.91357290000001</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>146.3391952666667</v>
+        <v>146.3391952666666</v>
       </c>
     </row>
     <row r="61">
@@ -1647,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>143.8720793571429</v>
+        <v>143.8720793571428</v>
       </c>
     </row>
     <row r="64">
@@ -1655,7 +1656,7 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>22.72147551612904</v>
+        <v>22.72147551612903</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -2159,7 +2160,7 @@
         <v>15.242472</v>
       </c>
       <c r="D28" t="n">
-        <v>10.716111</v>
+        <v>10.71611100000001</v>
       </c>
       <c r="E28" t="n">
         <v>126.199206</v>
@@ -2176,7 +2177,7 @@
         <v>15.226944</v>
       </c>
       <c r="D29" t="n">
-        <v>11.216388</v>
+        <v>11.21638799999999</v>
       </c>
       <c r="E29" t="n">
         <v>126.581559</v>
@@ -2295,7 +2296,7 @@
         <v>12.484222</v>
       </c>
       <c r="D36" t="n">
-        <v>59.358612</v>
+        <v>59.35861199999999</v>
       </c>
       <c r="E36" t="n">
         <v>171.600017</v>
@@ -2737,7 +2738,7 @@
         <v>11.19425</v>
       </c>
       <c r="D62" t="n">
-        <v>61.443055</v>
+        <v>61.44305499999999</v>
       </c>
       <c r="E62" t="n">
         <v>169.928516</v>
@@ -2805,7 +2806,7 @@
         <v>12.502472</v>
       </c>
       <c r="D66" t="n">
-        <v>99.285556</v>
+        <v>99.28555599999999</v>
       </c>
       <c r="E66" t="n">
         <v>204.272147</v>
@@ -3672,7 +3673,7 @@
         <v>3.382222</v>
       </c>
       <c r="D117" t="n">
-        <v>60.989167</v>
+        <v>60.98916699999999</v>
       </c>
       <c r="E117" t="n">
         <v>158.262066</v>
@@ -3740,7 +3741,7 @@
         <v>3.864111</v>
       </c>
       <c r="D121" t="n">
-        <v>63.751944</v>
+        <v>63.75194399999999</v>
       </c>
       <c r="E121" t="n">
         <v>161.016725</v>
@@ -6001,7 +6002,7 @@
         <v>4.191306</v>
       </c>
       <c r="D254" t="n">
-        <v>94.688889</v>
+        <v>94.68888899999999</v>
       </c>
       <c r="E254" t="n">
         <v>110.073895</v>
@@ -6902,7 +6903,7 @@
         <v>8.776806000000001</v>
       </c>
       <c r="D307" t="n">
-        <v>97.003334</v>
+        <v>97.00333400000001</v>
       </c>
       <c r="E307" t="n">
         <v>188.463189</v>
@@ -6973,7 +6974,7 @@
         <v>77.086945</v>
       </c>
       <c r="E311" t="n">
-        <v>168.6141380000001</v>
+        <v>168.614138</v>
       </c>
     </row>
     <row r="312">
@@ -7004,7 +7005,7 @@
         <v>8.733860999999999</v>
       </c>
       <c r="D313" t="n">
-        <v>92.11055500000001</v>
+        <v>92.11055499999999</v>
       </c>
       <c r="E313" t="n">
         <v>182.901238</v>
@@ -7276,7 +7277,7 @@
         <v>9.08625</v>
       </c>
       <c r="D329" t="n">
-        <v>99.49888900000001</v>
+        <v>99.49888899999999</v>
       </c>
       <c r="E329" t="n">
         <v>189.726051</v>
@@ -7395,7 +7396,7 @@
         <v>8.779166999999999</v>
       </c>
       <c r="D336" t="n">
-        <v>99.038889</v>
+        <v>99.03888900000001</v>
       </c>
       <c r="E336" t="n">
         <v>184.716254</v>
@@ -7871,7 +7872,7 @@
         <v>8.782556</v>
       </c>
       <c r="D364" t="n">
-        <v>50.165241</v>
+        <v>50.16524099999999</v>
       </c>
       <c r="E364" t="n">
         <v>138.683504</v>
@@ -7973,7 +7974,7 @@
         <v>9.350139</v>
       </c>
       <c r="D370" t="n">
-        <v>95.98777800000001</v>
+        <v>95.98777799999999</v>
       </c>
       <c r="E370" t="n">
         <v>184.45866</v>
@@ -8109,7 +8110,7 @@
         <v>8.520056</v>
       </c>
       <c r="D378" t="n">
-        <v>39.985278</v>
+        <v>39.98527799999999</v>
       </c>
       <c r="E378" t="n">
         <v>127.299034</v>
@@ -8721,7 +8722,7 @@
         <v>9.018556</v>
       </c>
       <c r="D414" t="n">
-        <v>30.656112</v>
+        <v>30.65611199999999</v>
       </c>
       <c r="E414" t="n">
         <v>112.625942</v>
@@ -8874,7 +8875,7 @@
         <v>8.833527999999999</v>
       </c>
       <c r="D423" t="n">
-        <v>92.13805499999999</v>
+        <v>92.13805500000001</v>
       </c>
       <c r="E423" t="n">
         <v>165.216546</v>
@@ -8942,7 +8943,7 @@
         <v>9.063389000000001</v>
       </c>
       <c r="D427" t="n">
-        <v>39.061945</v>
+        <v>39.06194499999999</v>
       </c>
       <c r="E427" t="n">
         <v>124.731624</v>
@@ -8993,7 +8994,7 @@
         <v>8.95025</v>
       </c>
       <c r="D430" t="n">
-        <v>92.266666</v>
+        <v>92.26666600000001</v>
       </c>
       <c r="E430" t="n">
         <v>177.580119</v>
@@ -9299,7 +9300,7 @@
         <v>8.497999999999999</v>
       </c>
       <c r="D448" t="n">
-        <v>96.081945</v>
+        <v>96.08194499999999</v>
       </c>
       <c r="E448" t="n">
         <v>180.082566</v>
@@ -9673,7 +9674,7 @@
         <v>8.2105</v>
       </c>
       <c r="D470" t="n">
-        <v>61.065556</v>
+        <v>61.06555599999999</v>
       </c>
       <c r="E470" t="n">
         <v>143.792972</v>
@@ -9979,7 +9980,7 @@
         <v>7.99725</v>
       </c>
       <c r="D488" t="n">
-        <v>94.748611</v>
+        <v>94.74861100000001</v>
       </c>
       <c r="E488" t="n">
         <v>176.398591</v>
@@ -10064,7 +10065,7 @@
         <v>8.332167</v>
       </c>
       <c r="D493" t="n">
-        <v>93.422222</v>
+        <v>93.42222199999999</v>
       </c>
       <c r="E493" t="n">
         <v>175.17947</v>
@@ -10319,7 +10320,7 @@
         <v>6.570806</v>
       </c>
       <c r="D508" t="n">
-        <v>95.90694499999999</v>
+        <v>95.90694500000001</v>
       </c>
       <c r="E508" t="n">
         <v>175.181752</v>
@@ -10421,7 +10422,7 @@
         <v>7.388306</v>
       </c>
       <c r="D514" t="n">
-        <v>99.76444499999999</v>
+        <v>99.76444500000001</v>
       </c>
       <c r="E514" t="n">
         <v>179.682779</v>
@@ -10815,7 +10816,7 @@
         <v>85.11250100000001</v>
       </c>
       <c r="E537" t="n">
-        <v>162.5914210000001</v>
+        <v>162.591421</v>
       </c>
     </row>
     <row r="538">
@@ -11118,7 +11119,7 @@
         <v>5.711861</v>
       </c>
       <c r="D555" t="n">
-        <v>90.352222</v>
+        <v>90.35222200000001</v>
       </c>
       <c r="E555" t="n">
         <v>166.900316</v>
@@ -11254,7 +11255,7 @@
         <v>4.584917</v>
       </c>
       <c r="D563" t="n">
-        <v>91.306389</v>
+        <v>91.30638900000001</v>
       </c>
       <c r="E563" t="n">
         <v>166.360262</v>
@@ -11818,7 +11819,7 @@
         <v>20.004721</v>
       </c>
       <c r="E596" t="n">
-        <v>94.807472</v>
+        <v>94.80747199999999</v>
       </c>
     </row>
     <row r="597">
@@ -11832,7 +11833,7 @@
         <v>6.287583</v>
       </c>
       <c r="D597" t="n">
-        <v>63.812778</v>
+        <v>63.81277799999999</v>
       </c>
       <c r="E597" t="n">
         <v>139.275097</v>
@@ -12019,7 +12020,7 @@
         <v>5.560583</v>
       </c>
       <c r="D608" t="n">
-        <v>49.315277</v>
+        <v>49.31527699999999</v>
       </c>
       <c r="E608" t="n">
         <v>123.285794</v>
@@ -12277,7 +12278,7 @@
         <v>48.07888899999999</v>
       </c>
       <c r="E623" t="n">
-        <v>128.9185079999999</v>
+        <v>128.918508</v>
       </c>
     </row>
     <row r="624">
@@ -12988,7 +12989,7 @@
         <v>7.502556</v>
       </c>
       <c r="D665" t="n">
-        <v>98.48694399999999</v>
+        <v>98.48694400000001</v>
       </c>
       <c r="E665" t="n">
         <v>176.88137</v>
@@ -13022,7 +13023,7 @@
         <v>6.929222</v>
       </c>
       <c r="D667" t="n">
-        <v>97.890278</v>
+        <v>97.89027800000001</v>
       </c>
       <c r="E667" t="n">
         <v>172.685088</v>
@@ -13124,7 +13125,7 @@
         <v>6.844139</v>
       </c>
       <c r="D673" t="n">
-        <v>98.88888799999999</v>
+        <v>98.88888800000001</v>
       </c>
       <c r="E673" t="n">
         <v>173.075631</v>
@@ -13243,7 +13244,7 @@
         <v>6.708278</v>
       </c>
       <c r="D680" t="n">
-        <v>93.831945</v>
+        <v>93.83194499999999</v>
       </c>
       <c r="E680" t="n">
         <v>167.419848</v>
@@ -14535,7 +14536,7 @@
         <v>5.914806</v>
       </c>
       <c r="D756" t="n">
-        <v>97.351389</v>
+        <v>97.35138900000001</v>
       </c>
       <c r="E756" t="n">
         <v>166.915192</v>
@@ -14552,7 +14553,7 @@
         <v>6.005222</v>
       </c>
       <c r="D757" t="n">
-        <v>96.73305499999999</v>
+        <v>96.73305500000001</v>
       </c>
       <c r="E757" t="n">
         <v>166.469437</v>
@@ -14688,7 +14689,7 @@
         <v>5.863639</v>
       </c>
       <c r="D765" t="n">
-        <v>99.51444499999999</v>
+        <v>99.51444500000001</v>
       </c>
       <c r="E765" t="n">
         <v>168.711108</v>
@@ -14756,7 +14757,7 @@
         <v>5.8535</v>
       </c>
       <c r="D769" t="n">
-        <v>95.087777</v>
+        <v>95.08777699999999</v>
       </c>
       <c r="E769" t="n">
         <v>163.588898</v>
@@ -14926,7 +14927,7 @@
         <v>5.7525</v>
       </c>
       <c r="D779" t="n">
-        <v>95.8575</v>
+        <v>95.85749999999999</v>
       </c>
       <c r="E779" t="n">
         <v>164.246603</v>
@@ -14963,7 +14964,7 @@
         <v>93.35166700000002</v>
       </c>
       <c r="E781" t="n">
-        <v>161.4637980000001</v>
+        <v>161.463798</v>
       </c>
     </row>
     <row r="782">
@@ -14977,7 +14978,7 @@
         <v>5.731778</v>
       </c>
       <c r="D782" t="n">
-        <v>95.048333</v>
+        <v>95.04833299999999</v>
       </c>
       <c r="E782" t="n">
         <v>163.11763</v>
@@ -15113,7 +15114,7 @@
         <v>5.721972</v>
       </c>
       <c r="D790" t="n">
-        <v>97.176389</v>
+        <v>97.17638899999999</v>
       </c>
       <c r="E790" t="n">
         <v>164.936875</v>
@@ -15130,7 +15131,7 @@
         <v>5.710278</v>
       </c>
       <c r="D791" t="n">
-        <v>92.142779</v>
+        <v>92.14277899999999</v>
       </c>
       <c r="E791" t="n">
         <v>159.883906</v>
@@ -15504,7 +15505,7 @@
         <v>5.565361</v>
       </c>
       <c r="D813" t="n">
-        <v>90.827223</v>
+        <v>90.82722299999999</v>
       </c>
       <c r="E813" t="n">
         <v>157.123286</v>
@@ -15521,7 +15522,7 @@
         <v>5.580917</v>
       </c>
       <c r="D814" t="n">
-        <v>90.355</v>
+        <v>90.35499999999999</v>
       </c>
       <c r="E814" t="n">
         <v>156.655423</v>
@@ -15691,7 +15692,7 @@
         <v>5.273861</v>
       </c>
       <c r="D824" t="n">
-        <v>94.76305499999999</v>
+        <v>94.76305500000001</v>
       </c>
       <c r="E824" t="n">
         <v>160.695833</v>
@@ -15810,7 +15811,7 @@
         <v>5.404667</v>
       </c>
       <c r="D831" t="n">
-        <v>91.448611</v>
+        <v>91.44861100000001</v>
       </c>
       <c r="E831" t="n">
         <v>157.106469</v>
@@ -16048,7 +16049,7 @@
         <v>4.83925</v>
       </c>
       <c r="D845" t="n">
-        <v>99.941388</v>
+        <v>99.94138799999999</v>
       </c>
       <c r="E845" t="n">
         <v>163.632927</v>
@@ -16119,7 +16120,7 @@
         <v>105.078656</v>
       </c>
       <c r="E849" t="n">
-        <v>169.3936770000001</v>
+        <v>169.393677</v>
       </c>
     </row>
     <row r="850">
@@ -16150,7 +16151,7 @@
         <v>4.616639</v>
       </c>
       <c r="D851" t="n">
-        <v>94.27722300000001</v>
+        <v>94.27722299999999</v>
       </c>
       <c r="E851" t="n">
         <v>158.294281</v>
@@ -16184,7 +16185,7 @@
         <v>4.658694</v>
       </c>
       <c r="D853" t="n">
-        <v>96.14361100000001</v>
+        <v>96.14361099999999</v>
       </c>
       <c r="E853" t="n">
         <v>160.019133</v>
@@ -16269,7 +16270,7 @@
         <v>4.611028</v>
       </c>
       <c r="D858" t="n">
-        <v>94.42611100000001</v>
+        <v>94.42611099999999</v>
       </c>
       <c r="E858" t="n">
         <v>157.753582</v>
@@ -16558,7 +16559,7 @@
         <v>4.692111</v>
       </c>
       <c r="D875" t="n">
-        <v>44.358333</v>
+        <v>44.35833299999999</v>
       </c>
       <c r="E875" t="n">
         <v>108.239937</v>
@@ -16898,7 +16899,7 @@
         <v>4.494528</v>
       </c>
       <c r="D895" t="n">
-        <v>93.05249999999999</v>
+        <v>93.05250000000001</v>
       </c>
       <c r="E895" t="n">
         <v>156.054224</v>
@@ -17102,7 +17103,7 @@
         <v>4.419028</v>
       </c>
       <c r="D907" t="n">
-        <v>94.946389</v>
+        <v>94.94638900000001</v>
       </c>
       <c r="E907" t="n">
         <v>157.004443</v>
@@ -17238,7 +17239,7 @@
         <v>4.404306</v>
       </c>
       <c r="D915" t="n">
-        <v>98.911389</v>
+        <v>98.91138899999999</v>
       </c>
       <c r="E915" t="n">
         <v>160.670717</v>
@@ -17442,7 +17443,7 @@
         <v>0</v>
       </c>
       <c r="D927" t="n">
-        <v>98.849722</v>
+        <v>98.84972199999999</v>
       </c>
       <c r="E927" t="n">
         <v>155.871291</v>
@@ -17544,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="D933" t="n">
-        <v>98.91194400000001</v>
+        <v>98.91194399999999</v>
       </c>
       <c r="E933" t="n">
         <v>155.538572</v>
@@ -17731,7 +17732,7 @@
         <v>0</v>
       </c>
       <c r="D944" t="n">
-        <v>91.42777700000001</v>
+        <v>91.42777699999999</v>
       </c>
       <c r="E944" t="n">
         <v>147.787302</v>
@@ -17748,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="D945" t="n">
-        <v>97.33416699999999</v>
+        <v>97.33416700000001</v>
       </c>
       <c r="E945" t="n">
         <v>153.676571</v>
@@ -17782,7 +17783,7 @@
         <v>0</v>
       </c>
       <c r="D947" t="n">
-        <v>93.362499</v>
+        <v>93.36249899999999</v>
       </c>
       <c r="E947" t="n">
         <v>149.4121</v>
@@ -17938,7 +17939,7 @@
         <v>123.9075</v>
       </c>
       <c r="E956" t="n">
-        <v>176.7469479999999</v>
+        <v>176.746948</v>
       </c>
     </row>
     <row r="957">
@@ -17986,7 +17987,7 @@
         <v>0</v>
       </c>
       <c r="D959" t="n">
-        <v>96.929722</v>
+        <v>96.92972200000001</v>
       </c>
       <c r="E959" t="n">
         <v>152.8225</v>
@@ -18054,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="D963" t="n">
-        <v>96.755</v>
+        <v>96.75500000000001</v>
       </c>
       <c r="E963" t="n">
         <v>152.578285</v>
@@ -18156,7 +18157,7 @@
         <v>0</v>
       </c>
       <c r="D969" t="n">
-        <v>59.442222</v>
+        <v>59.44222199999999</v>
       </c>
       <c r="E969" t="n">
         <v>115.042559</v>
@@ -18326,7 +18327,7 @@
         <v>0</v>
       </c>
       <c r="D979" t="n">
-        <v>98.458611</v>
+        <v>98.45861099999999</v>
       </c>
       <c r="E979" t="n">
         <v>153.510813</v>
@@ -18822,7 +18823,7 @@
         <v>92.91694499999998</v>
       </c>
       <c r="E1008" t="n">
-        <v>146.1864519999999</v>
+        <v>146.186452</v>
       </c>
     </row>
     <row r="1009">
@@ -19329,7 +19330,7 @@
         <v>0</v>
       </c>
       <c r="D1038" t="n">
-        <v>99.82305599999999</v>
+        <v>99.82305600000001</v>
       </c>
       <c r="E1038" t="n">
         <v>152.148871</v>
@@ -19601,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="D1054" t="n">
-        <v>90.16083399999999</v>
+        <v>90.16083400000001</v>
       </c>
       <c r="E1054" t="n">
         <v>142.484073</v>
@@ -19839,7 +19840,7 @@
         <v>0</v>
       </c>
       <c r="D1068" t="n">
-        <v>135.3475000000001</v>
+        <v>135.3475</v>
       </c>
       <c r="E1068" t="n">
         <v>187.661595</v>
@@ -20298,7 +20299,7 @@
         <v>0</v>
       </c>
       <c r="D1095" t="n">
-        <v>132.5250009999999</v>
+        <v>132.525001</v>
       </c>
       <c r="E1095" t="n">
         <v>184.952907</v>
@@ -20998,7 +20999,7 @@
         <v>137.507222</v>
       </c>
       <c r="E1136" t="n">
-        <v>189.6695910000001</v>
+        <v>189.669591</v>
       </c>
     </row>
     <row r="1137">
@@ -21947,7 +21948,7 @@
         <v>0</v>
       </c>
       <c r="D1192" t="n">
-        <v>96.60166700000001</v>
+        <v>96.60166699999999</v>
       </c>
       <c r="E1192" t="n">
         <v>147.333201</v>
@@ -22253,7 +22254,7 @@
         <v>0</v>
       </c>
       <c r="D1210" t="n">
-        <v>94.96388899999999</v>
+        <v>94.96388900000001</v>
       </c>
       <c r="E1210" t="n">
         <v>144.726254</v>
@@ -22627,7 +22628,7 @@
         <v>0</v>
       </c>
       <c r="D1232" t="n">
-        <v>99.79000000000001</v>
+        <v>99.78999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>139.142973</v>
@@ -22746,7 +22747,7 @@
         <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>93.84388800000001</v>
+        <v>93.84388799999999</v>
       </c>
       <c r="E1239" t="n">
         <v>134.117266</v>
@@ -22967,7 +22968,7 @@
         <v>0</v>
       </c>
       <c r="D1252" t="n">
-        <v>97.51777800000001</v>
+        <v>97.51777799999999</v>
       </c>
       <c r="E1252" t="n">
         <v>137.295765</v>
@@ -23103,7 +23104,7 @@
         <v>0</v>
       </c>
       <c r="D1260" t="n">
-        <v>93.639444</v>
+        <v>93.63944400000001</v>
       </c>
       <c r="E1260" t="n">
         <v>133.079235</v>
@@ -23239,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="D1268" t="n">
-        <v>94.163611</v>
+        <v>94.16361099999999</v>
       </c>
       <c r="E1268" t="n">
         <v>133.521945</v>
@@ -23990,7 +23991,7 @@
         <v>102.081666</v>
       </c>
       <c r="E1312" t="n">
-        <v>148.2938930000001</v>
+        <v>148.293893</v>
       </c>
     </row>
     <row r="1313">
@@ -24055,7 +24056,7 @@
         <v>0</v>
       </c>
       <c r="D1316" t="n">
-        <v>53.759444</v>
+        <v>53.75944399999999</v>
       </c>
       <c r="E1316" t="n">
         <v>100.946834</v>
@@ -24446,7 +24447,7 @@
         <v>0</v>
       </c>
       <c r="D1339" t="n">
-        <v>95.788889</v>
+        <v>95.78888900000001</v>
       </c>
       <c r="E1339" t="n">
         <v>142.903247</v>
@@ -24684,7 +24685,7 @@
         <v>0</v>
       </c>
       <c r="D1353" t="n">
-        <v>90.238333</v>
+        <v>90.23833300000001</v>
       </c>
       <c r="E1353" t="n">
         <v>138.097051</v>
@@ -24752,7 +24753,7 @@
         <v>0</v>
       </c>
       <c r="D1357" t="n">
-        <v>99.589444</v>
+        <v>99.58944400000001</v>
       </c>
       <c r="E1357" t="n">
         <v>147.274388</v>
@@ -24956,7 +24957,7 @@
         <v>0</v>
       </c>
       <c r="D1369" t="n">
-        <v>91.113333</v>
+        <v>91.11333300000001</v>
       </c>
       <c r="E1369" t="n">
         <v>138.56983</v>
@@ -25126,7 +25127,7 @@
         <v>0</v>
       </c>
       <c r="D1379" t="n">
-        <v>97.021666</v>
+        <v>97.02166600000001</v>
       </c>
       <c r="E1379" t="n">
         <v>144.314025</v>
@@ -25432,7 +25433,7 @@
         <v>0</v>
       </c>
       <c r="D1397" t="n">
-        <v>92.88</v>
+        <v>92.88000000000001</v>
       </c>
       <c r="E1397" t="n">
         <v>140.112587</v>
@@ -25619,7 +25620,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>99.752222</v>
+        <v>99.75222199999999</v>
       </c>
       <c r="E1408" t="n">
         <v>146.490298</v>
@@ -25755,7 +25756,7 @@
         <v>0</v>
       </c>
       <c r="D1416" t="n">
-        <v>143.2133339999999</v>
+        <v>143.213334</v>
       </c>
       <c r="E1416" t="n">
         <v>189.741956</v>
@@ -26520,7 +26521,7 @@
         <v>0</v>
       </c>
       <c r="D1461" t="n">
-        <v>90.532222</v>
+        <v>90.53222199999999</v>
       </c>
       <c r="E1461" t="n">
         <v>135.935164</v>
@@ -26540,7 +26541,7 @@
         <v>61.56944399999999</v>
       </c>
       <c r="E1462" t="n">
-        <v>97.278085</v>
+        <v>97.27808499999999</v>
       </c>
     </row>
     <row r="1463">
@@ -26659,7 +26660,7 @@
         <v>138.352222</v>
       </c>
       <c r="E1469" t="n">
-        <v>183.7047810000001</v>
+        <v>183.704781</v>
       </c>
     </row>
     <row r="1470">
@@ -27438,7 +27439,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>93.953889</v>
+        <v>93.95388899999999</v>
       </c>
       <c r="E1515" t="n">
         <v>138.387581</v>
@@ -27659,7 +27660,7 @@
         <v>0</v>
       </c>
       <c r="D1528" t="n">
-        <v>98.081667</v>
+        <v>98.08166700000001</v>
       </c>
       <c r="E1528" t="n">
         <v>142.132554</v>
@@ -28121,7 +28122,7 @@
         <v>115.263333</v>
       </c>
       <c r="E1555" t="n">
-        <v>158.5333539999999</v>
+        <v>158.533354</v>
       </c>
     </row>
     <row r="1556">
@@ -28169,7 +28170,7 @@
         <v>0</v>
       </c>
       <c r="D1558" t="n">
-        <v>93.476112</v>
+        <v>93.47611200000001</v>
       </c>
       <c r="E1558" t="n">
         <v>130.606802</v>
@@ -28781,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="D1594" t="n">
-        <v>97.887221</v>
+        <v>97.88722100000001</v>
       </c>
       <c r="E1594" t="n">
         <v>140.333633</v>
@@ -29019,7 +29020,7 @@
         <v>0</v>
       </c>
       <c r="D1608" t="n">
-        <v>90.491666</v>
+        <v>90.49166600000001</v>
       </c>
       <c r="E1608" t="n">
         <v>132.68796</v>
@@ -29294,7 +29295,7 @@
         <v>55.59777800000001</v>
       </c>
       <c r="E1624" t="n">
-        <v>98.28368399999999</v>
+        <v>98.28368400000001</v>
       </c>
     </row>
     <row r="1625">
@@ -29410,7 +29411,7 @@
         <v>0</v>
       </c>
       <c r="D1631" t="n">
-        <v>91.98611099999999</v>
+        <v>91.98611100000001</v>
       </c>
       <c r="E1631" t="n">
         <v>133.898904</v>
@@ -30022,10 +30023,10 @@
         <v>0</v>
       </c>
       <c r="D1667" t="n">
-        <v>56.001111</v>
+        <v>56.00111099999999</v>
       </c>
       <c r="E1667" t="n">
-        <v>96.81899</v>
+        <v>96.81898999999999</v>
       </c>
     </row>
     <row r="1668">
@@ -30209,7 +30210,7 @@
         <v>0</v>
       </c>
       <c r="D1678" t="n">
-        <v>95.62388</v>
+        <v>95.62387999999999</v>
       </c>
       <c r="E1678" t="n">
         <v>135.842671</v>
@@ -30464,7 +30465,7 @@
         <v>0</v>
       </c>
       <c r="D1693" t="n">
-        <v>98.76000000000001</v>
+        <v>98.75999999999999</v>
       </c>
       <c r="E1693" t="n">
         <v>138.230395</v>
@@ -30739,7 +30740,7 @@
         <v>58.53166699999999</v>
       </c>
       <c r="E1709" t="n">
-        <v>98.54938900000001</v>
+        <v>98.54938899999999</v>
       </c>
     </row>
     <row r="1710">
@@ -30855,7 +30856,7 @@
         <v>0</v>
       </c>
       <c r="D1716" t="n">
-        <v>92.482778</v>
+        <v>92.48277800000001</v>
       </c>
       <c r="E1716" t="n">
         <v>131.524854</v>
@@ -31246,7 +31247,7 @@
         <v>0</v>
       </c>
       <c r="D1739" t="n">
-        <v>92.063333</v>
+        <v>92.06333300000001</v>
       </c>
       <c r="E1739" t="n">
         <v>131.575085</v>
@@ -31620,7 +31621,7 @@
         <v>0</v>
       </c>
       <c r="D1761" t="n">
-        <v>95.216666</v>
+        <v>95.21666599999999</v>
       </c>
       <c r="E1761" t="n">
         <v>134.314946</v>
@@ -32521,7 +32522,7 @@
         <v>0</v>
       </c>
       <c r="D1814" t="n">
-        <v>99.259445</v>
+        <v>99.25944500000001</v>
       </c>
       <c r="E1814" t="n">
         <v>136.641028</v>
@@ -32538,7 +32539,7 @@
         <v>0</v>
       </c>
       <c r="D1815" t="n">
-        <v>92.703334</v>
+        <v>92.70333400000001</v>
       </c>
       <c r="E1815" t="n">
         <v>130.404768</v>
@@ -32708,7 +32709,7 @@
         <v>0</v>
       </c>
       <c r="D1825" t="n">
-        <v>94.24722199999999</v>
+        <v>94.24722200000001</v>
       </c>
       <c r="E1825" t="n">
         <v>131.768007</v>
@@ -34289,7 +34290,7 @@
         <v>0</v>
       </c>
       <c r="D1918" t="n">
-        <v>93.04944500000001</v>
+        <v>93.04944499999999</v>
       </c>
       <c r="E1918" t="n">
         <v>129.650269</v>
@@ -34428,7 +34429,7 @@
         <v>60.443333</v>
       </c>
       <c r="E1926" t="n">
-        <v>96.97426900000001</v>
+        <v>96.97426899999999</v>
       </c>
     </row>
     <row r="1927">
@@ -34476,7 +34477,7 @@
         <v>0</v>
       </c>
       <c r="D1929" t="n">
-        <v>93.584808</v>
+        <v>93.58480800000001</v>
       </c>
       <c r="E1929" t="n">
         <v>129.950173</v>
@@ -34527,7 +34528,7 @@
         <v>0</v>
       </c>
       <c r="D1932" t="n">
-        <v>97.39277800000001</v>
+        <v>97.39277799999999</v>
       </c>
       <c r="E1932" t="n">
         <v>133.31692</v>
@@ -34595,7 +34596,7 @@
         <v>0</v>
       </c>
       <c r="D1936" t="n">
-        <v>96.13722199999999</v>
+        <v>96.13722200000001</v>
       </c>
       <c r="E1936" t="n">
         <v>132.808236</v>
@@ -34850,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="D1951" t="n">
-        <v>92.02888900000001</v>
+        <v>92.02888899999999</v>
       </c>
       <c r="E1951" t="n">
         <v>127.863713</v>
@@ -35516,7 +35517,7 @@
         <v>127.03361</v>
       </c>
       <c r="E1990" t="n">
-        <v>161.9780610000001</v>
+        <v>161.978061</v>
       </c>
     </row>
     <row r="1991">
@@ -35802,7 +35803,7 @@
         <v>0</v>
       </c>
       <c r="D2007" t="n">
-        <v>98.397778</v>
+        <v>98.39777799999999</v>
       </c>
       <c r="E2007" t="n">
         <v>132.939686</v>
@@ -36023,7 +36024,7 @@
         <v>0</v>
       </c>
       <c r="D2020" t="n">
-        <v>96.08749899999999</v>
+        <v>96.08749900000001</v>
       </c>
       <c r="E2020" t="n">
         <v>130.333201</v>
@@ -36635,10 +36636,10 @@
         <v>0</v>
       </c>
       <c r="D2056" t="n">
-        <v>61.725</v>
+        <v>61.72499999999999</v>
       </c>
       <c r="E2056" t="n">
-        <v>97.04447</v>
+        <v>97.04446999999999</v>
       </c>
     </row>
     <row r="2057">
@@ -36771,7 +36772,7 @@
         <v>0</v>
       </c>
       <c r="D2064" t="n">
-        <v>94.111667</v>
+        <v>94.11166700000001</v>
       </c>
       <c r="E2064" t="n">
         <v>130.0541</v>
@@ -36808,7 +36809,7 @@
         <v>61.101111</v>
       </c>
       <c r="E2066" t="n">
-        <v>96.94438100000001</v>
+        <v>96.94438099999999</v>
       </c>
     </row>
     <row r="2067">
@@ -36924,7 +36925,7 @@
         <v>0</v>
       </c>
       <c r="D2073" t="n">
-        <v>99.591667</v>
+        <v>99.59166699999999</v>
       </c>
       <c r="E2073" t="n">
         <v>134.498901</v>
@@ -37148,7 +37149,7 @@
         <v>64.56472199999999</v>
       </c>
       <c r="E2086" t="n">
-        <v>98.79825200000001</v>
+        <v>98.79825199999999</v>
       </c>
     </row>
     <row r="2087">
@@ -37230,7 +37231,7 @@
         <v>0</v>
       </c>
       <c r="D2091" t="n">
-        <v>97.2975</v>
+        <v>97.29749999999999</v>
       </c>
       <c r="E2091" t="n">
         <v>131.331533</v>
@@ -37352,7 +37353,7 @@
         <v>65.488056</v>
       </c>
       <c r="E2098" t="n">
-        <v>99.237264</v>
+        <v>99.23726400000001</v>
       </c>
     </row>
     <row r="2099">
@@ -37519,7 +37520,7 @@
         <v>0</v>
       </c>
       <c r="D2108" t="n">
-        <v>97.363056</v>
+        <v>97.36305599999999</v>
       </c>
       <c r="E2108" t="n">
         <v>130.829437</v>
@@ -38848,7 +38849,7 @@
         <v>57.95750000000001</v>
       </c>
       <c r="E2186" t="n">
-        <v>90.791991</v>
+        <v>90.79199100000001</v>
       </c>
     </row>
     <row r="2187">
@@ -38862,7 +38863,7 @@
         <v>0</v>
       </c>
       <c r="D2187" t="n">
-        <v>90.433611</v>
+        <v>90.43361100000001</v>
       </c>
       <c r="E2187" t="n">
         <v>123.161403</v>
@@ -38899,7 +38900,7 @@
         <v>64.7225</v>
       </c>
       <c r="E2189" t="n">
-        <v>97.42606600000001</v>
+        <v>97.42606599999999</v>
       </c>
     </row>
     <row r="2190">
@@ -38933,7 +38934,7 @@
         <v>66.53277700000001</v>
       </c>
       <c r="E2191" t="n">
-        <v>99.190202</v>
+        <v>99.19020200000001</v>
       </c>
     </row>
     <row r="2192">
@@ -39100,7 +39101,7 @@
         <v>0</v>
       </c>
       <c r="D2201" t="n">
-        <v>162.5366660000001</v>
+        <v>162.536666</v>
       </c>
       <c r="E2201" t="n">
         <v>195.145609</v>
@@ -39545,7 +39546,7 @@
         <v>67.17083299999999</v>
       </c>
       <c r="E2227" t="n">
-        <v>99.55941</v>
+        <v>99.55940999999999</v>
       </c>
     </row>
     <row r="2228">
@@ -40205,7 +40206,7 @@
         <v>0</v>
       </c>
       <c r="D2266" t="n">
-        <v>99.27889</v>
+        <v>99.27888999999999</v>
       </c>
       <c r="E2266" t="n">
         <v>130.81873</v>
@@ -40599,7 +40600,7 @@
         <v>65.73611099999999</v>
       </c>
       <c r="E2289" t="n">
-        <v>96.342696</v>
+        <v>96.34269599999999</v>
       </c>
     </row>
     <row r="2290">
@@ -40616,7 +40617,7 @@
         <v>65.515833</v>
       </c>
       <c r="E2290" t="n">
-        <v>98.085975</v>
+        <v>98.08597499999999</v>
       </c>
     </row>
     <row r="2291">
@@ -40681,7 +40682,7 @@
         <v>0</v>
       </c>
       <c r="D2294" t="n">
-        <v>90.227221</v>
+        <v>90.22722100000001</v>
       </c>
       <c r="E2294" t="n">
         <v>122.642521</v>
@@ -41191,7 +41192,7 @@
         <v>0</v>
       </c>
       <c r="D2324" t="n">
-        <v>95.918333</v>
+        <v>95.91833299999999</v>
       </c>
       <c r="E2324" t="n">
         <v>127.67437</v>
@@ -41310,10 +41311,10 @@
         <v>0</v>
       </c>
       <c r="D2331" t="n">
-        <v>97.11</v>
+        <v>97.11000000000001</v>
       </c>
       <c r="E2331" t="n">
-        <v>128.9598130000001</v>
+        <v>128.959813</v>
       </c>
     </row>
     <row r="2332">
@@ -41480,7 +41481,7 @@
         <v>0</v>
       </c>
       <c r="D2341" t="n">
-        <v>94.97749899999999</v>
+        <v>94.97749900000001</v>
       </c>
       <c r="E2341" t="n">
         <v>126.568136</v>
@@ -41565,7 +41566,7 @@
         <v>0</v>
       </c>
       <c r="D2346" t="n">
-        <v>95.00277699999999</v>
+        <v>95.00277700000001</v>
       </c>
       <c r="E2346" t="n">
         <v>126.485436</v>
@@ -41905,7 +41906,7 @@
         <v>0</v>
       </c>
       <c r="D2366" t="n">
-        <v>95.72666700000001</v>
+        <v>95.72666699999999</v>
       </c>
       <c r="E2366" t="n">
         <v>126.963799</v>
@@ -42024,7 +42025,7 @@
         <v>0</v>
       </c>
       <c r="D2373" t="n">
-        <v>97.16333299999999</v>
+        <v>97.16333300000001</v>
       </c>
       <c r="E2373" t="n">
         <v>121.495419</v>
@@ -42058,7 +42059,7 @@
         <v>0</v>
       </c>
       <c r="D2375" t="n">
-        <v>93.12472200000001</v>
+        <v>93.12472199999999</v>
       </c>
       <c r="E2375" t="n">
         <v>125.692778</v>
@@ -42330,7 +42331,7 @@
         <v>0</v>
       </c>
       <c r="D2391" t="n">
-        <v>90.882222</v>
+        <v>90.88222200000001</v>
       </c>
       <c r="E2391" t="n">
         <v>122.227116</v>
@@ -42466,7 +42467,7 @@
         <v>0</v>
       </c>
       <c r="D2399" t="n">
-        <v>93.78777700000001</v>
+        <v>93.78777699999999</v>
       </c>
       <c r="E2399" t="n">
         <v>124.774654</v>
@@ -42500,7 +42501,7 @@
         <v>0</v>
       </c>
       <c r="D2401" t="n">
-        <v>96.605555</v>
+        <v>96.60555500000001</v>
       </c>
       <c r="E2401" t="n">
         <v>127.555265</v>
@@ -42789,7 +42790,7 @@
         <v>0</v>
       </c>
       <c r="D2418" t="n">
-        <v>93.177222</v>
+        <v>93.17722200000001</v>
       </c>
       <c r="E2418" t="n">
         <v>124.055949</v>
@@ -42942,7 +42943,7 @@
         <v>0</v>
       </c>
       <c r="D2427" t="n">
-        <v>92.41194400000001</v>
+        <v>92.41194399999999</v>
       </c>
       <c r="E2427" t="n">
         <v>122.990139</v>
@@ -43336,7 +43337,7 @@
         <v>65.61361000000001</v>
       </c>
       <c r="E2450" t="n">
-        <v>95.633786</v>
+        <v>95.63378600000001</v>
       </c>
     </row>
     <row r="2451">
@@ -44064,7 +44065,7 @@
         <v>0</v>
       </c>
       <c r="D2493" t="n">
-        <v>93.95</v>
+        <v>93.94999999999999</v>
       </c>
       <c r="E2493" t="n">
         <v>123.770089</v>
@@ -44084,7 +44085,7 @@
         <v>140.624444</v>
       </c>
       <c r="E2494" t="n">
-        <v>170.5125530000001</v>
+        <v>170.512553</v>
       </c>
     </row>
     <row r="2495">
@@ -45016,7 +45017,7 @@
         <v>0</v>
       </c>
       <c r="D2549" t="n">
-        <v>93.984723</v>
+        <v>93.98472299999999</v>
       </c>
       <c r="E2549" t="n">
         <v>123.160698</v>
@@ -48317,7 +48318,7 @@
         <v>65.889166</v>
       </c>
       <c r="E2743" t="n">
-        <v>92.503767</v>
+        <v>92.50376700000001</v>
       </c>
     </row>
     <row r="2744">
@@ -48351,7 +48352,7 @@
         <v>66.101389</v>
       </c>
       <c r="E2745" t="n">
-        <v>92.63888300000001</v>
+        <v>92.63888299999999</v>
       </c>
     </row>
     <row r="2746">
@@ -48929,7 +48930,7 @@
         <v>69.78361099999999</v>
       </c>
       <c r="E2779" t="n">
-        <v>95.861422</v>
+        <v>95.86142199999999</v>
       </c>
     </row>
     <row r="2780">
@@ -49286,7 +49287,7 @@
         <v>66.54507700000001</v>
       </c>
       <c r="E2800" t="n">
-        <v>92.033992</v>
+        <v>92.03399200000001</v>
       </c>
     </row>
     <row r="2801">
